--- a/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254512986675825</v>
+        <v>1.265047139542393</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58820465909156</v>
+        <v>4.648444698224144</v>
       </c>
       <c r="D3" t="n">
-        <v>6.053068647977295</v>
+        <v>6.180087165952748</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89578629374468</v>
+        <v>12.09357900371928</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378026124042106</v>
+        <v>1.409516109420813</v>
       </c>
       <c r="C4" t="n">
-        <v>5.027396225262443</v>
+        <v>5.164702522411371</v>
       </c>
       <c r="D4" t="n">
-        <v>6.279923119392309</v>
+        <v>6.490513827265038</v>
       </c>
       <c r="E4" t="n">
-        <v>12.68534546869686</v>
+        <v>13.06473245909722</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.542327851789464</v>
+        <v>1.600542420142009</v>
       </c>
       <c r="C5" t="n">
-        <v>5.586800577620861</v>
+        <v>5.804718003311661</v>
       </c>
       <c r="D5" t="n">
-        <v>6.566264971989431</v>
+        <v>6.856485481639957</v>
       </c>
       <c r="E5" t="n">
-        <v>13.69539340139976</v>
+        <v>14.26174590509363</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.737518480462318</v>
+        <v>1.817515595090311</v>
       </c>
       <c r="C6" t="n">
-        <v>6.333006967496549</v>
+        <v>6.56901203745991</v>
       </c>
       <c r="D6" t="n">
-        <v>6.875102142331445</v>
+        <v>7.339775610844939</v>
       </c>
       <c r="E6" t="n">
-        <v>14.94562759029031</v>
+        <v>15.72630324339516</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.969799418635231</v>
+        <v>2.053322997399587</v>
       </c>
       <c r="C7" t="n">
-        <v>7.228424434370211</v>
+        <v>7.43052885706205</v>
       </c>
       <c r="D7" t="n">
-        <v>7.322047806155973</v>
+        <v>7.787938690565594</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52027165916142</v>
+        <v>17.27179054502723</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.211919130734602</v>
+        <v>1.252261075534048</v>
       </c>
       <c r="C8" t="n">
-        <v>5.024080675186666</v>
+        <v>5.002399620949648</v>
       </c>
       <c r="D8" t="n">
-        <v>5.571163475117889</v>
+        <v>6.030399175719255</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80716328103916</v>
+        <v>12.28505987220295</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.519141731059017</v>
+        <v>1.561467314338124</v>
       </c>
       <c r="C9" t="n">
-        <v>6.281519417543825</v>
+        <v>6.062019186289541</v>
       </c>
       <c r="D9" t="n">
-        <v>6.123709648767102</v>
+        <v>6.588001436182836</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92437079736994</v>
+        <v>14.2114879368105</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.835364675366859</v>
+        <v>1.887772044939986</v>
       </c>
       <c r="C10" t="n">
-        <v>7.723891944031012</v>
+        <v>7.277180582520042</v>
       </c>
       <c r="D10" t="n">
-        <v>6.640430639032448</v>
+        <v>7.218449921449759</v>
       </c>
       <c r="E10" t="n">
-        <v>16.19968725843032</v>
+        <v>16.38340254890979</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.165455607215968</v>
+        <v>2.219776676356109</v>
       </c>
       <c r="C11" t="n">
-        <v>9.280102949497651</v>
+        <v>8.593910603278468</v>
       </c>
       <c r="D11" t="n">
-        <v>7.229263015330651</v>
+        <v>7.877235266756949</v>
       </c>
       <c r="E11" t="n">
-        <v>18.67482157204427</v>
+        <v>18.69092254639153</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.491699820396772</v>
+        <v>2.551571415004755</v>
       </c>
       <c r="C12" t="n">
-        <v>10.91165358260208</v>
+        <v>9.986083295145766</v>
       </c>
       <c r="D12" t="n">
-        <v>7.751608169086717</v>
+        <v>8.440603340972483</v>
       </c>
       <c r="E12" t="n">
-        <v>21.15496157208556</v>
+        <v>20.978258051123</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.808110880209473</v>
+        <v>2.874068335961705</v>
       </c>
       <c r="C13" t="n">
-        <v>12.569914269405</v>
+        <v>11.4831048526564</v>
       </c>
       <c r="D13" t="n">
-        <v>8.256494609878619</v>
+        <v>8.986157590559209</v>
       </c>
       <c r="E13" t="n">
-        <v>23.63451975949309</v>
+        <v>23.34333077917731</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.6258625555261</v>
+        <v>1.665014653971463</v>
       </c>
       <c r="C14" t="n">
-        <v>8.705883386857611</v>
+        <v>8.142262029849517</v>
       </c>
       <c r="D14" t="n">
-        <v>6.301779608698021</v>
+        <v>6.785575059873806</v>
       </c>
       <c r="E14" t="n">
-        <v>16.63352555108173</v>
+        <v>16.59285174369479</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.662167585629147</v>
+        <v>1.694368910328443</v>
       </c>
       <c r="C15" t="n">
-        <v>9.459934346058459</v>
+        <v>8.797509900094964</v>
       </c>
       <c r="D15" t="n">
-        <v>6.344092934751059</v>
+        <v>6.854984622564056</v>
       </c>
       <c r="E15" t="n">
-        <v>17.46619486643867</v>
+        <v>17.34686343298746</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.917804870337974</v>
+        <v>1.957241675617569</v>
       </c>
       <c r="C16" t="n">
-        <v>11.20345936393854</v>
+        <v>10.40732088065663</v>
       </c>
       <c r="D16" t="n">
-        <v>6.790896132430825</v>
+        <v>7.386218122809049</v>
       </c>
       <c r="E16" t="n">
-        <v>19.91216036670734</v>
+        <v>19.75078067908325</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.531330069084175</v>
+        <v>1.561891875117378</v>
       </c>
       <c r="C17" t="n">
-        <v>10.35663324668637</v>
+        <v>9.626890360642671</v>
       </c>
       <c r="D17" t="n">
-        <v>6.309191803865085</v>
+        <v>6.895501350318323</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19715511963563</v>
+        <v>18.08428358607837</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.73588702074104</v>
+        <v>1.77128884295618</v>
       </c>
       <c r="C18" t="n">
-        <v>12.05611706255394</v>
+        <v>11.25973314234597</v>
       </c>
       <c r="D18" t="n">
-        <v>6.727995557019732</v>
+        <v>7.407345333404439</v>
       </c>
       <c r="E18" t="n">
-        <v>20.51999964031471</v>
+        <v>20.43836731870658</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.732450903776177</v>
+        <v>1.769403887364026</v>
       </c>
       <c r="C19" t="n">
-        <v>12.86024697214841</v>
+        <v>12.06206645364167</v>
       </c>
       <c r="D19" t="n">
-        <v>6.821811367637558</v>
+        <v>7.551092832260257</v>
       </c>
       <c r="E19" t="n">
-        <v>21.41450924356215</v>
+        <v>21.38256317326595</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.921702408723834</v>
+        <v>1.963318693906856</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79912996569657</v>
+        <v>13.93103919317041</v>
       </c>
       <c r="D20" t="n">
-        <v>7.243795983353963</v>
+        <v>7.998043292095661</v>
       </c>
       <c r="E20" t="n">
-        <v>23.96462835777436</v>
+        <v>23.89240117917292</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.13743325518627</v>
+        <v>1.16488292099701</v>
       </c>
       <c r="C21" t="n">
-        <v>10.85111011288436</v>
+        <v>10.32377415102523</v>
       </c>
       <c r="D21" t="n">
-        <v>6.048606510726854</v>
+        <v>6.688146417704354</v>
       </c>
       <c r="E21" t="n">
-        <v>18.03714987879748</v>
+        <v>18.17680348972659</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.265047139542393</v>
+        <v>1.288923243709676</v>
       </c>
       <c r="C3" t="n">
-        <v>4.648444698224144</v>
+        <v>4.610775038812194</v>
       </c>
       <c r="D3" t="n">
-        <v>6.180087165952748</v>
+        <v>6.039687426768411</v>
       </c>
       <c r="E3" t="n">
-        <v>12.09357900371928</v>
+        <v>11.93938570929028</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.409516109420813</v>
+        <v>1.480120380581519</v>
       </c>
       <c r="C4" t="n">
-        <v>5.164702522411371</v>
+        <v>5.077946395138711</v>
       </c>
       <c r="D4" t="n">
-        <v>6.490513827265038</v>
+        <v>6.232081670858214</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06473245909722</v>
+        <v>12.79014844657844</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.600542420142009</v>
+        <v>1.728045866487171</v>
       </c>
       <c r="C5" t="n">
-        <v>5.804718003311661</v>
+        <v>5.64686113968075</v>
       </c>
       <c r="D5" t="n">
-        <v>6.856485481639957</v>
+        <v>6.518438009537508</v>
       </c>
       <c r="E5" t="n">
-        <v>14.26174590509363</v>
+        <v>13.89334501570543</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.817515595090311</v>
+        <v>1.998828815344548</v>
       </c>
       <c r="C6" t="n">
-        <v>6.56901203745991</v>
+        <v>6.339382418318691</v>
       </c>
       <c r="D6" t="n">
-        <v>7.339775610844939</v>
+        <v>6.87280343548866</v>
       </c>
       <c r="E6" t="n">
-        <v>15.72630324339516</v>
+        <v>15.2110146691519</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.053322997399587</v>
+        <v>2.285900706917661</v>
       </c>
       <c r="C7" t="n">
-        <v>7.43052885706205</v>
+        <v>7.122994248181857</v>
       </c>
       <c r="D7" t="n">
-        <v>7.787938690565594</v>
+        <v>7.2131913881962</v>
       </c>
       <c r="E7" t="n">
-        <v>17.27179054502723</v>
+        <v>16.62208634329572</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.252261075534048</v>
+        <v>1.447402035953452</v>
       </c>
       <c r="C8" t="n">
-        <v>5.002399620949648</v>
+        <v>4.710045126262772</v>
       </c>
       <c r="D8" t="n">
-        <v>6.030399175719255</v>
+        <v>5.471590389873314</v>
       </c>
       <c r="E8" t="n">
-        <v>12.28505987220295</v>
+        <v>11.62903755208954</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.561467314338124</v>
+        <v>1.838667535950934</v>
       </c>
       <c r="C9" t="n">
-        <v>6.062019186289541</v>
+        <v>5.678550868160118</v>
       </c>
       <c r="D9" t="n">
-        <v>6.588001436182836</v>
+        <v>5.913813730479525</v>
       </c>
       <c r="E9" t="n">
-        <v>14.2114879368105</v>
+        <v>13.43103213459058</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.887772044939986</v>
+        <v>2.261118675332905</v>
       </c>
       <c r="C10" t="n">
-        <v>7.277180582520042</v>
+        <v>6.805078025354787</v>
       </c>
       <c r="D10" t="n">
-        <v>7.218449921449759</v>
+        <v>6.338061636666805</v>
       </c>
       <c r="E10" t="n">
-        <v>16.38340254890979</v>
+        <v>15.4042583373545</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.219776676356109</v>
+        <v>2.71665486342674</v>
       </c>
       <c r="C11" t="n">
-        <v>8.593910603278468</v>
+        <v>8.066366820901411</v>
       </c>
       <c r="D11" t="n">
-        <v>7.877235266756949</v>
+        <v>6.767218499715418</v>
       </c>
       <c r="E11" t="n">
-        <v>18.69092254639153</v>
+        <v>17.55024018404357</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.551571415004755</v>
+        <v>3.189073337149932</v>
       </c>
       <c r="C12" t="n">
-        <v>9.986083295145766</v>
+        <v>9.48798573441297</v>
       </c>
       <c r="D12" t="n">
-        <v>8.440603340972483</v>
+        <v>7.253281417536181</v>
       </c>
       <c r="E12" t="n">
-        <v>20.978258051123</v>
+        <v>19.93034048909908</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.874068335961705</v>
+        <v>3.642876622920037</v>
       </c>
       <c r="C13" t="n">
-        <v>11.4831048526564</v>
+        <v>10.99795131120884</v>
       </c>
       <c r="D13" t="n">
-        <v>8.986157590559209</v>
+        <v>7.682251900809853</v>
       </c>
       <c r="E13" t="n">
-        <v>23.34333077917731</v>
+        <v>22.32307983493873</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.665014653971463</v>
+        <v>2.107203637441269</v>
       </c>
       <c r="C14" t="n">
-        <v>8.142262029849517</v>
+        <v>7.854600135028159</v>
       </c>
       <c r="D14" t="n">
-        <v>6.785575059873806</v>
+        <v>5.854897871201915</v>
       </c>
       <c r="E14" t="n">
-        <v>16.59285174369479</v>
+        <v>15.81670164367134</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.694368910328443</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="C15" t="n">
-        <v>8.797509900094964</v>
+        <v>8.567250793540918</v>
       </c>
       <c r="D15" t="n">
-        <v>6.854984622564056</v>
+        <v>5.828194333646402</v>
       </c>
       <c r="E15" t="n">
-        <v>17.34686343298746</v>
+        <v>16.58474250765771</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.957241675617569</v>
+        <v>2.576155063328843</v>
       </c>
       <c r="C16" t="n">
-        <v>10.40732088065663</v>
+        <v>10.19742322148866</v>
       </c>
       <c r="D16" t="n">
-        <v>7.386218122809049</v>
+        <v>6.252279889449897</v>
       </c>
       <c r="E16" t="n">
-        <v>19.75078067908325</v>
+        <v>19.0258581742674</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.561891875117378</v>
+        <v>2.081648744699724</v>
       </c>
       <c r="C17" t="n">
-        <v>9.626890360642671</v>
+        <v>9.508305055446698</v>
       </c>
       <c r="D17" t="n">
-        <v>6.895501350318323</v>
+        <v>5.779980703890841</v>
       </c>
       <c r="E17" t="n">
-        <v>18.08428358607837</v>
+        <v>17.36993450403726</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.77128884295618</v>
+        <v>2.409346310900268</v>
       </c>
       <c r="C18" t="n">
-        <v>11.25973314234597</v>
+        <v>11.17029592648908</v>
       </c>
       <c r="D18" t="n">
-        <v>7.407345333404439</v>
+        <v>6.151611479856429</v>
       </c>
       <c r="E18" t="n">
-        <v>20.43836731870658</v>
+        <v>19.73125371724578</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.769403887364026</v>
+        <v>2.445896777929376</v>
       </c>
       <c r="C19" t="n">
-        <v>12.06206645364167</v>
+        <v>12.01021053990335</v>
       </c>
       <c r="D19" t="n">
-        <v>7.551092832260257</v>
+        <v>6.224987303271836</v>
       </c>
       <c r="E19" t="n">
-        <v>21.38256317326595</v>
+        <v>20.68109462110457</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.963318693906856</v>
+        <v>2.754018294907238</v>
       </c>
       <c r="C20" t="n">
-        <v>13.93103919317041</v>
+        <v>13.828073493949</v>
       </c>
       <c r="D20" t="n">
-        <v>7.998043292095661</v>
+        <v>6.575628313320626</v>
       </c>
       <c r="E20" t="n">
-        <v>23.89240117917292</v>
+        <v>23.15772010217687</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.16488292099701</v>
+        <v>1.654735755507999</v>
       </c>
       <c r="C21" t="n">
-        <v>10.32377415102523</v>
+        <v>10.16493718995514</v>
       </c>
       <c r="D21" t="n">
-        <v>6.688146417704354</v>
+        <v>5.44966187131996</v>
       </c>
       <c r="E21" t="n">
-        <v>18.17680348972659</v>
+        <v>17.2693348167831</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_74_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.288923243709676</v>
+        <v>2.604026402535939</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610775038812194</v>
+        <v>7.676547540742463</v>
       </c>
       <c r="D3" t="n">
-        <v>6.039687426768411</v>
+        <v>8.16919899191147</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93938570929028</v>
+        <v>18.44977293518987</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.480120380581519</v>
+        <v>1.108683255202332</v>
       </c>
       <c r="C4" t="n">
-        <v>5.077946395138711</v>
+        <v>4.430694329244413</v>
       </c>
       <c r="D4" t="n">
-        <v>6.232081670858214</v>
+        <v>5.71385053788434</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79014844657844</v>
+        <v>11.25322812233109</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.728045866487171</v>
+        <v>1.24362521666734</v>
       </c>
       <c r="C5" t="n">
-        <v>5.64686113968075</v>
+        <v>5.045175142743202</v>
       </c>
       <c r="D5" t="n">
-        <v>6.518438009537508</v>
+        <v>5.948168666747643</v>
       </c>
       <c r="E5" t="n">
-        <v>13.89334501570543</v>
+        <v>12.23696902615819</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.998828815344548</v>
+        <v>1.396555839158669</v>
       </c>
       <c r="C6" t="n">
-        <v>6.339382418318691</v>
+        <v>5.847151349919655</v>
       </c>
       <c r="D6" t="n">
-        <v>6.87280343548866</v>
+        <v>6.260498769799532</v>
       </c>
       <c r="E6" t="n">
-        <v>15.2110146691519</v>
+        <v>13.50420595887786</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.285900706917661</v>
+        <v>1.548401206758155</v>
       </c>
       <c r="C7" t="n">
-        <v>7.122994248181857</v>
+        <v>6.906528039072451</v>
       </c>
       <c r="D7" t="n">
-        <v>7.2131913881962</v>
+        <v>6.573131784309908</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62208634329572</v>
+        <v>15.02806103014051</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.447402035953452</v>
+        <v>1.708475318348261</v>
       </c>
       <c r="C8" t="n">
-        <v>4.710045126262772</v>
+        <v>8.154638579852557</v>
       </c>
       <c r="D8" t="n">
-        <v>5.471590389873314</v>
+        <v>7.00329446725281</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62903755208954</v>
+        <v>16.86640836545363</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.838667535950934</v>
+        <v>1.862407694457753</v>
       </c>
       <c r="C9" t="n">
-        <v>5.678550868160118</v>
+        <v>9.555879101131746</v>
       </c>
       <c r="D9" t="n">
-        <v>5.913813730479525</v>
+        <v>7.473717241071173</v>
       </c>
       <c r="E9" t="n">
-        <v>13.43103213459058</v>
+        <v>18.89200403666067</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.261118675332905</v>
+        <v>1.146160992277024</v>
       </c>
       <c r="C10" t="n">
-        <v>6.805078025354787</v>
+        <v>7.068249676357591</v>
       </c>
       <c r="D10" t="n">
-        <v>6.338061636666805</v>
+        <v>5.907077761682633</v>
       </c>
       <c r="E10" t="n">
-        <v>15.4042583373545</v>
+        <v>14.12148843031725</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.71665486342674</v>
+        <v>1.091634724783156</v>
       </c>
       <c r="C11" t="n">
-        <v>8.066366820901411</v>
+        <v>7.651604162221045</v>
       </c>
       <c r="D11" t="n">
-        <v>6.767218499715418</v>
+        <v>5.787510708782414</v>
       </c>
       <c r="E11" t="n">
-        <v>17.55024018404357</v>
+        <v>14.53074959578661</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.189073337149932</v>
+        <v>1.193068897585936</v>
       </c>
       <c r="C12" t="n">
-        <v>9.48798573441297</v>
+        <v>9.117598921587595</v>
       </c>
       <c r="D12" t="n">
-        <v>7.253281417536181</v>
+        <v>6.149952326236251</v>
       </c>
       <c r="E12" t="n">
-        <v>19.93034048909908</v>
+        <v>16.46062014540978</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.642876622920037</v>
+        <v>0.945560483868273</v>
       </c>
       <c r="C13" t="n">
-        <v>10.99795131120884</v>
+        <v>8.726637533325388</v>
       </c>
       <c r="D13" t="n">
-        <v>7.682251900809853</v>
+        <v>5.60718329046636</v>
       </c>
       <c r="E13" t="n">
-        <v>22.32307983493873</v>
+        <v>15.27938130766002</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.107203637441269</v>
+        <v>1.034408651102609</v>
       </c>
       <c r="C14" t="n">
-        <v>7.854600135028159</v>
+        <v>10.21319990709591</v>
       </c>
       <c r="D14" t="n">
-        <v>5.854897871201915</v>
+        <v>6.001168461657647</v>
       </c>
       <c r="E14" t="n">
-        <v>15.81670164367134</v>
+        <v>17.24877701985617</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.189297380470387</v>
+        <v>1.008461059279366</v>
       </c>
       <c r="C15" t="n">
-        <v>8.567250793540918</v>
+        <v>10.9977537674677</v>
       </c>
       <c r="D15" t="n">
-        <v>5.828194333646402</v>
+        <v>6.081387066571654</v>
       </c>
       <c r="E15" t="n">
-        <v>16.58474250765771</v>
+        <v>18.08760189331873</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.576155063328843</v>
+        <v>1.101815448476195</v>
       </c>
       <c r="C16" t="n">
-        <v>10.19742322148866</v>
+        <v>12.76479164286449</v>
       </c>
       <c r="D16" t="n">
-        <v>6.252279889449897</v>
+        <v>6.482980782470855</v>
       </c>
       <c r="E16" t="n">
-        <v>19.0258581742674</v>
+        <v>20.34958787381154</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.081648744699724</v>
+        <v>0.6581342084959343</v>
       </c>
       <c r="C17" t="n">
-        <v>9.508305055446698</v>
+        <v>9.457313079688118</v>
       </c>
       <c r="D17" t="n">
-        <v>5.779980703890841</v>
+        <v>5.401840940646098</v>
       </c>
       <c r="E17" t="n">
-        <v>17.36993450403726</v>
+        <v>15.51728822883015</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.409346310900268</v>
+        <v>0.5233500661798898</v>
       </c>
       <c r="C18" t="n">
-        <v>11.17029592648908</v>
+        <v>8.354034827132597</v>
       </c>
       <c r="D18" t="n">
-        <v>6.151611479856429</v>
+        <v>4.94480793188808</v>
       </c>
       <c r="E18" t="n">
-        <v>19.73125371724578</v>
+        <v>13.82219282520057</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.445896777929376</v>
+        <v>0.6175487584023712</v>
       </c>
       <c r="C19" t="n">
-        <v>12.01021053990335</v>
+        <v>10.28189279396206</v>
       </c>
       <c r="D19" t="n">
-        <v>6.224987303271836</v>
+        <v>5.504129233951573</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68109462110457</v>
+        <v>16.403570786316</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.754018294907238</v>
+        <v>0.710117749435803</v>
       </c>
       <c r="C20" t="n">
-        <v>13.828073493949</v>
+        <v>12.29676305981891</v>
       </c>
       <c r="D20" t="n">
-        <v>6.575628313320626</v>
+        <v>6.119851941624044</v>
       </c>
       <c r="E20" t="n">
-        <v>23.15772010217687</v>
+        <v>19.12673275087876</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.654735755507999</v>
+        <v>0.7991131788257763</v>
       </c>
       <c r="C21" t="n">
-        <v>10.16493718995514</v>
+        <v>14.31846628969733</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44966187131996</v>
+        <v>6.648905961965608</v>
       </c>
       <c r="E21" t="n">
-        <v>17.2693348167831</v>
+        <v>21.76648543048871</v>
       </c>
     </row>
   </sheetData>
